--- a/0_Data/1_Household Data/1_Vietnam/3_Matching_Tables/Item_Fuel_Concordance_Vietnam.xlsx
+++ b/0_Data/1_Household Data/1_Vietnam/3_Matching_Tables/Item_Fuel_Concordance_Vietnam.xlsx
@@ -14,7 +14,7 @@
   <sheets>
     <sheet name="Item_Vietnam" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="162913" concurrentCalc="0"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
   <si>
     <t>Electricity</t>
   </si>
@@ -51,9 +51,6 @@
   </si>
   <si>
     <t>LPG</t>
-  </si>
-  <si>
-    <t>Charcoal</t>
   </si>
 </sst>
 </file>
@@ -371,7 +368,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C10"/>
+  <dimension ref="A1:E9"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="14.26953125" bestFit="1" customWidth="1"/>
@@ -384,15 +381,18 @@
     <col min="43" max="75" width="6" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>8</v>
       </c>
       <c r="B1">
+        <v>208</v>
+      </c>
+      <c r="C1">
         <v>209</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>7</v>
       </c>
@@ -400,26 +400,29 @@
         <v>204</v>
       </c>
       <c r="C2">
+        <v>205</v>
+      </c>
+      <c r="D2">
         <v>206</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="E2">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>6</v>
       </c>
       <c r="B3">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>5</v>
       </c>
-      <c r="B4">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -427,43 +430,35 @@
         <v>207</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>3</v>
       </c>
-      <c r="B6">
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>2</v>
+      </c>
+      <c r="B7">
+        <v>202</v>
+      </c>
+      <c r="C7">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>1</v>
+      </c>
+      <c r="B8">
         <v>210</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A7" t="s">
-        <v>9</v>
-      </c>
-      <c r="B7">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A8" t="s">
-        <v>2</v>
-      </c>
-      <c r="B8">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B9">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A10" t="s">
-        <v>0</v>
-      </c>
-      <c r="B10">
         <v>1024</v>
       </c>
     </row>
